--- a/uploads/PLANILLA DATOS.xlsx
+++ b/uploads/PLANILLA DATOS.xlsx
@@ -1,29 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\SISTEMA(PLANTILLAS)\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PLANILLA DE DATA TELEFONICA " sheetId="1" r:id="rId1"/>
+    <sheet name="PLANILLA DE DATA TELEFONICA " sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="listadelitos" localSheetId="0">[2]DELITOS!$A$2:$A$41</definedName>
-    <definedName name="LISTAEMPRESA" localSheetId="0">[2]EMPRESA!$A$2:$A$5</definedName>
-    <definedName name="LISTAEMPRESA">[1]EMPRESA!$A$2:$A$5</definedName>
+    <definedName function="false" hidden="false" name="LISTAEMPRESA" vbProcedure="false">[1]EMPRESA!$A$2:$A$5</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="listadelitos" vbProcedure="false">[2]DELITOS!$A$2:$A$41</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="LISTAEMPRESA" vbProcedure="false">[2]EMPRESA!$A$2:$A$5</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -35,74 +31,76 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>Nro de Solicitud</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Despacho   Solicitante</t>
-  </si>
-  <si>
-    <t>N°   Actas   Procesales</t>
-  </si>
-  <si>
-    <t>Dato Solicitado</t>
-  </si>
-  <si>
-    <t>Desde</t>
-  </si>
-  <si>
-    <t>Hasta</t>
-  </si>
-  <si>
-    <t>Credencial</t>
-  </si>
-  <si>
-    <t>Delito</t>
-  </si>
-  <si>
-    <t>Fiscal que conoce la causa</t>
-  </si>
-  <si>
-    <t>Teléfono Funcionario Investigador</t>
-  </si>
-  <si>
-    <t>{SOLICITUD}</t>
-  </si>
-  <si>
-    <t>{FECHA}</t>
-  </si>
-  <si>
-    <t>{DM}</t>
-  </si>
-  <si>
-    <t>{EXP}</t>
-  </si>
-  <si>
-    <t>{INFO_R}</t>
-  </si>
-  <si>
-    <t>{DESDE}</t>
-  </si>
-  <si>
-    <t>{HASTA}</t>
-  </si>
-  <si>
-    <t>{delito}</t>
-  </si>
-  <si>
-    <t>{FISCAL}</t>
+    <t xml:space="preserve">Nro de Solicitud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Despacho   Solicitante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N°   Actas   Procesales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dato Solicitado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal que conoce la causa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teléfono Funcionario Investigador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{SOLICITUD}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{FECHA}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{DM}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{EXP}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{INFO_R}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{DESDE}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{HASTA}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{delito}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{FISCAL}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d/mm/yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="d/mm/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,7 +109,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <color theme="0"/>
       <name val="Tahoma"/>
@@ -119,7 +132,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Tahoma"/>
@@ -148,7 +161,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -171,93 +184,144 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -316,42 +380,26 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF262626"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="EMPRESA"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Entes"/>
@@ -376,54 +424,54 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -455,7 +503,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -479,7 +527,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -539,36 +587,37 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="136" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="136"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
@@ -603,7 +652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
         <v>11</v>
       </c>
@@ -625,7 +674,7 @@
       <c r="H2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="15" t="n">
         <v>29991</v>
       </c>
       <c r="J2" s="11" t="s">
@@ -634,13 +683,13 @@
       <c r="K2" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="18">
+      <c r="L2" s="17" t="n">
         <v>4168140567</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="18"/>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="19"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
@@ -652,8 +701,8 @@
       <c r="K3" s="20"/>
       <c r="L3" s="20"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="18"/>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="17"/>
       <c r="C4" s="19"/>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -665,8 +714,8 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="18"/>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="17"/>
       <c r="C5" s="19"/>
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
@@ -678,8 +727,8 @@
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="18"/>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="17"/>
       <c r="C6" s="19"/>
       <c r="D6" s="20"/>
       <c r="E6" s="20"/>
@@ -691,8 +740,8 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="18"/>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="17"/>
       <c r="C7" s="19"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
@@ -704,8 +753,8 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="18"/>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="17"/>
       <c r="C8" s="19"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
@@ -717,8 +766,8 @@
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="17"/>
       <c r="C9" s="19"/>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -730,8 +779,8 @@
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="17"/>
       <c r="C10" s="19"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
@@ -743,8 +792,8 @@
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="18"/>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="17"/>
       <c r="C11" s="19"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
@@ -757,7 +806,12 @@
       <c r="L11" s="20"/>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>